--- a/business-libraries/test-data/student_case/output_template.xlsx
+++ b/business-libraries/test-data/student_case/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL-ST-RED-SUMMARY</v>
+        <v>STUDENT_CASE_TPL_L3_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>student_case</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>L3</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>评估显示，您在「${维度名1}」和「${维度名2}」两个维度上的得分同时处于高危水平。行为与情绪双重危机，需要优先关注。</v>
+        <v>本次筛查结果达到 L3 专业会商层级，最突出的是「${主要归因}」。请整理时间线、已尝试措施和效果，并启动转介流程。在专业介入前，保持日常陪伴和安全环境。</v>
       </c>
       <c r="F2" t="str">
-        <v>${维度名1} ${维度名2} 会被替换为实际触发红线的维度中文名</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL-ST-RED-CONCLUSION</v>
+        <v>STUDENT_CASE_TPL_L2_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>student_case</v>
       </c>
       <c r="C3" t="str">
-        <v>red</v>
+        <v>L2</v>
       </c>
       <c r="D3" t="str">
-        <v>conclusion</v>
+        <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次评估结论：${主归因}（${次归因}）。已触发安全熔断，常规建议暂停输出。</v>
+        <v>本次筛查结果为 L2 年级协同层级，主要归因是「${主要归因}」，同时「${次要归因}」也需要关注。建议整理协同材料并与年级组共同制定支持方案。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主归因} 来自归因-分级规则.主归因；${次归因} 来自归因-分级规则.次归因</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,99 +470,30 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL-ST-RED-GOAL</v>
+        <v>STUDENT_CASE_TPL_L1_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>student_case</v>
       </c>
       <c r="C4" t="str">
-        <v>red</v>
+        <v>L1</v>
       </c>
       <c r="D4" t="str">
-        <v>goal</v>
+        <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>当前首要目标：1) 确保教师获得即时心理支持 2) 降低当前的急性压力水平 3) 建立至少一个可依赖的支持关系</v>
+        <v>本次筛查结果为 L1 教师支持层级，主要落在「${主要归因}」。处理重点是先做教育场景下的结构化观察，区分表现、诱因和已尝试支持，不做标签判断。</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>TPL-ST-ORANGE-ATTRIBUTION</v>
-      </c>
-      <c r="B5" t="str">
-        <v>student_case</v>
-      </c>
-      <c r="C5" t="str">
-        <v>orange</v>
-      </c>
-      <c r="D5" t="str">
-        <v>attribution</v>
-      </c>
-      <c r="E5" t="str">
-        <v>本次评估的归因分析：${主归因}。建议重点关注以下方面：${工具标签}</v>
-      </c>
-      <c r="F5" t="str">
-        <v>${主归因} ${工具标签} 从归因规则中取值</v>
-      </c>
-      <c r="G5" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>TPL-ST-ORANGE-ACTION</v>
-      </c>
-      <c r="B6" t="str">
-        <v>student_case</v>
-      </c>
-      <c r="C6" t="str">
-        <v>orange</v>
-      </c>
-      <c r="D6" t="str">
-        <v>action</v>
-      </c>
-      <c r="E6" t="str">
-        <v>根据评估结果，建议采取以下行动：${输出动作摘要}。推荐工具：${输出工具摘要}。</v>
-      </c>
-      <c r="F6" t="str">
-        <v>${输出动作摘要} ${输出工具摘要} 从归因规则中取值</v>
-      </c>
-      <c r="G6" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>TPL-ST-GREEN-SUMMARY</v>
-      </c>
-      <c r="B7" t="str">
-        <v>student_case</v>
-      </c>
-      <c r="C7" t="str">
-        <v>green</v>
-      </c>
-      <c r="D7" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E7" t="str">
-        <v>本次评估结果整体良好，各项指标均在正常范围内。继续保持现有节奏。</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/student_case/output_template.xlsx
+++ b/business-libraries/test-data/student_case/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>STUDENT_CASE_TPL_L3_SUMMARY</v>
+        <v>TPL_SC_RED_1</v>
       </c>
       <c r="B2" t="str">
         <v>student_case</v>
       </c>
       <c r="C2" t="str">
-        <v>L3</v>
+        <v>red</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
@@ -439,7 +439,7 @@
         <v>本次筛查结果达到 L3 专业会商层级，最突出的是「${主要归因}」。请整理时间线、已尝试措施和效果，并启动转介流程。在专业介入前，保持日常陪伴和安全环境。</v>
       </c>
       <c r="F2" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>STUDENT_CASE_TPL_L2_SUMMARY</v>
+        <v>TPL_SC_ORANGE_2</v>
       </c>
       <c r="B3" t="str">
         <v>student_case</v>
       </c>
       <c r="C3" t="str">
-        <v>L2</v>
+        <v>orange</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
@@ -462,7 +462,7 @@
         <v>本次筛查结果为 L2 年级协同层级，主要归因是「${主要归因}」，同时「${次要归因}」也需要关注。建议整理协同材料并与年级组共同制定支持方案。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,30 +470,53 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>STUDENT_CASE_TPL_L1_SUMMARY</v>
+        <v>TPL_SC_YELLOW_3</v>
       </c>
       <c r="B4" t="str">
         <v>student_case</v>
       </c>
       <c r="C4" t="str">
-        <v>L1</v>
+        <v>yellow</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>本次筛查结果为 L1 教师支持层级，主要落在「${主要归因}」。处理重点是先做教育场景下的结构化观察，区分表现、诱因和已尝试支持，不做标签判断。</v>
+        <v>学生当前信号以关注为主，建议按推荐工具做日常支持，两周后复评。</v>
       </c>
       <c r="F4" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TPL_SC_DEFAULT</v>
+      </c>
+      <c r="B5" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C5" t="str">
+        <v>green</v>
+      </c>
+      <c r="D5" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E5" t="str">
+        <v>本次筛查结果为 L1 教师支持层级，主要落在「${主要归因}」。处理重点是先做教育场景下的结构化观察，区分表现、诱因和已尝试支持，不做标签判断。</v>
+      </c>
+      <c r="F5" t="str">
+        <v>兜底模板：命中未覆盖等级时使用</v>
+      </c>
+      <c r="G5" t="str">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/student_case/output_template.xlsx
+++ b/business-libraries/test-data/student_case/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL_SC_RED_1</v>
+        <v>STUDENT_CASE_TPL_L3_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>student_case</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>L3</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
@@ -439,7 +439,7 @@
         <v>本次筛查结果达到 L3 专业会商层级，最突出的是「${主要归因}」。请整理时间线、已尝试措施和效果，并启动转介流程。在专业介入前，保持日常陪伴和安全环境。</v>
       </c>
       <c r="F2" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL_SC_ORANGE_2</v>
+        <v>STUDENT_CASE_TPL_L2_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>student_case</v>
       </c>
       <c r="C3" t="str">
-        <v>orange</v>
+        <v>L2</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
@@ -462,7 +462,7 @@
         <v>本次筛查结果为 L2 年级协同层级，主要归因是「${主要归因}」，同时「${次要归因}」也需要关注。建议整理协同材料并与年级组共同制定支持方案。</v>
       </c>
       <c r="F3" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,53 +470,30 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL_SC_YELLOW_3</v>
+        <v>STUDENT_CASE_TPL_L1_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>student_case</v>
       </c>
       <c r="C4" t="str">
-        <v>yellow</v>
+        <v>L1</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>学生当前信号以关注为主，建议按推荐工具做日常支持，两周后复评。</v>
+        <v>本次筛查结果为 L1 教师支持层级，主要落在「${主要归因}」。处理重点是先做教育场景下的结构化观察，区分表现、诱因和已尝试支持，不做标签判断。</v>
       </c>
       <c r="F4" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>TPL_SC_DEFAULT</v>
-      </c>
-      <c r="B5" t="str">
-        <v>student_case</v>
-      </c>
-      <c r="C5" t="str">
-        <v>green</v>
-      </c>
-      <c r="D5" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E5" t="str">
-        <v>本次筛查结果为 L1 教师支持层级，主要落在「${主要归因}」。处理重点是先做教育场景下的结构化观察，区分表现、诱因和已尝试支持，不做标签判断。</v>
-      </c>
-      <c r="F5" t="str">
-        <v>兜底模板：命中未覆盖等级时使用</v>
-      </c>
-      <c r="G5" t="str">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/student_case/output_template.xlsx
+++ b/business-libraries/test-data/student_case/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,7 +436,7 @@
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>本次筛查结果达到 L3 专业会商层级，最突出的是「${主要归因}」。请整理时间线、已尝试措施和效果，并启动转介流程。在专业介入前，保持日常陪伴和安全环境。</v>
+        <v>本次评估触发红色·紧急响应（安全防护题 1「体罚/暴力/忽视」或题 2「被欺凌/排斥」≥4 分）。请立即：①暂停常规评估与学业干预；②启动学校安全流程，通知年级组长与德育处；③做好家校安全沟通；④24 小时内完成安全评估与安全计划。保持学生处于有人陪伴的安全环境，不让学生独处。转介心理健康中心前请整理观察事实，不写诊断结论。</v>
       </c>
       <c r="F2" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -459,7 +459,7 @@
         <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次筛查结果为 L2 年级协同层级，主要归因是「${主要归因}」，同时「${次要归因}」也需要关注。建议整理协同材料并与年级组共同制定支持方案。</v>
+        <v>本次评估判定为橙色·高响应：≥3 个编码激活，或含 B/C 类编码且六维 D/E 维度≥3。请启动 L3 中心会商（心理教师主导，校领导+年级组长+班主任多角色协同），48 小时内完成 S2 全方位评估并制定综合干预方案，纳入年级组周例会讨论。</v>
       </c>
       <c r="F3" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -482,7 +482,7 @@
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>学生当前信号以关注为主，建议按推荐工具做日常支持，两周后复评。</v>
+        <v>本次评估判定为黄色·中响应：≥2 个编码激活且无安全信号。请启动 L2 年级协同（年级组长+班主任，必要时心理教师参与），1 周内完成 S2 分层评估并制定组合处方，按双周记录进展。</v>
       </c>
       <c r="F4" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -493,30 +493,76 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TPL_SC_DEFAULT</v>
+        <v>TPL_SC_BLUE_4</v>
       </c>
       <c r="B5" t="str">
         <v>student_case</v>
       </c>
       <c r="C5" t="str">
-        <v>green</v>
+        <v>blue</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>本次筛查结果为 L1 教师支持层级，主要落在「${主要归因}」。处理重点是先做教育场景下的结构化观察，区分表现、诱因和已尝试支持，不做标签判断。</v>
+        <v>本次评估判定为蓝色·低风险：仅 1 个编码激活（非 E 类）或六维仅 1 个维度 D/E。请按标准诊疗流程启动 L1 班级自主干预，使用对应干预技术（见处方库），1 个月内完成标准诊疗流程并按月记录进展。</v>
       </c>
       <c r="F5" t="str">
+        <v>可用占位符见 ⑩ 说明</v>
+      </c>
+      <c r="G5" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TPL_SC_DEFAULT_5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C6" t="str">
+        <v>green</v>
+      </c>
+      <c r="D6" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E6" t="str">
+        <v>本次评估判定为紫色·待观察：无编码激活、无能力缺损。请纳入 S0 优势通道：安排优势测评（1-2 年级 50 题版/3-6 年级 20 题版），制定优势发展目标，每学期复查五维筛查一次；后续出现信号则转入 S1-S5 流程。</v>
+      </c>
+      <c r="F6" t="str">
+        <v>可用占位符见 ⑩ 说明</v>
+      </c>
+      <c r="G6" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TPL_SC_DEFAULT</v>
+      </c>
+      <c r="B7" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="C7" t="str">
+        <v>green</v>
+      </c>
+      <c r="D7" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E7" t="str">
+        <v>本次评估未发现需要重点干预的信号，当前状态相对平稳。建议保持现有节奏，按每学期一次频率复查；若后续出现异常表现，可随时重新评估。</v>
+      </c>
+      <c r="F7" t="str">
         <v>兜底模板：命中未覆盖等级时使用</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G7" t="str">
         <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>